--- a/registro/plantillas/Plantilla Cursos Extension.xlsx
+++ b/registro/plantillas/Plantilla Cursos Extension.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planeacionenap\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE3F1F2-2E59-4501-AE47-5CBC6DFB2426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{EAE3F1F2-2E59-4501-AE47-5CBC6DFB2426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E323A6B-1757-4C0A-A108-16D3AF8DC887}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3761,7 +3761,7 @@
       <c r="Z3" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="yBE3/x8hlpSNnnAkU+Ut1BahMoGQbgbJGzBfxkN3AgWwUDK60+S8P/J1ZMAsVepG1qaB6GwoDLN8q7TQEsTqOA==" saltValue="9sNR2iJDp+80bsxTGeG8+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="0G9aT2KO4U+ra/F2FhRSinphf1B5Nk0szMK1uXuQ4JRdheyD7b+B5GVPKzcAz3bO+iFo2/ZREOmOXYkZn+O6ow==" saltValue="io24qmImXCUye35TaZJnAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
@@ -3775,7 +3775,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -3785,20 +3785,17 @@
           </x14:formula2>
           <xm:sqref>I3</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
-          <x14:formula1>
-            <xm:f>Parameters!$D$4:$D$238</xm:f>
-          </x14:formula1>
-          <x14:formula2>
-            <xm:f>0</xm:f>
-          </x14:formula2>
-          <xm:sqref>E3</xm:sqref>
-        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB72A587-D260-4AA8-9EF6-BEAED64FBFE4}">
           <x14:formula1>
             <xm:f>Parameters!$I$4:$I$7</xm:f>
           </x14:formula1>
           <xm:sqref>O3:O1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C5707996-09ED-4471-A7A6-7040A0CC14FC}">
+          <x14:formula1>
+            <xm:f>Parameters!$D$4:$D$238</xm:f>
+          </x14:formula1>
+          <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>

--- a/registro/plantillas/Plantilla Cursos Extension.xlsx
+++ b/registro/plantillas/Plantilla Cursos Extension.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://escuelanaval-my.sharepoint.com/personal/jestadisticaplen_enap_edu_co/Documents/Estadística/Plantillas Xertify/Plantillas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\planeacionenap\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3" documentId="13_ncr:1_{EAE3F1F2-2E59-4501-AE47-5CBC6DFB2426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1E323A6B-1757-4C0A-A108-16D3AF8DC887}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EAE3F1F2-2E59-4501-AE47-5CBC6DFB2426}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3761,7 +3761,7 @@
       <c r="Z3" s="29"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="0G9aT2KO4U+ra/F2FhRSinphf1B5Nk0szMK1uXuQ4JRdheyD7b+B5GVPKzcAz3bO+iFo2/ZREOmOXYkZn+O6ow==" saltValue="io24qmImXCUye35TaZJnAQ==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection algorithmName="SHA-512" hashValue="yBE3/x8hlpSNnnAkU+Ut1BahMoGQbgbJGzBfxkN3AgWwUDK60+S8P/J1ZMAsVepG1qaB6GwoDLN8q7TQEsTqOA==" saltValue="9sNR2iJDp+80bsxTGeG8+w==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <protectedRanges>
     <protectedRange sqref="A3:Z422" name="Rango1"/>
   </protectedRanges>
@@ -3775,7 +3775,7 @@
   <drawing r:id="rId2"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" disablePrompts="1" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000000000000}">
           <x14:formula1>
             <xm:f>Parameters!$F$4:$F$5</xm:f>
@@ -3785,17 +3785,20 @@
           </x14:formula2>
           <xm:sqref>I3</xm:sqref>
         </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{00000000-0002-0000-0000-000001000000}">
+          <x14:formula1>
+            <xm:f>Parameters!$D$4:$D$238</xm:f>
+          </x14:formula1>
+          <x14:formula2>
+            <xm:f>0</xm:f>
+          </x14:formula2>
+          <xm:sqref>E3</xm:sqref>
+        </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{FB72A587-D260-4AA8-9EF6-BEAED64FBFE4}">
           <x14:formula1>
             <xm:f>Parameters!$I$4:$I$7</xm:f>
           </x14:formula1>
           <xm:sqref>O3:O1048576</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{C5707996-09ED-4471-A7A6-7040A0CC14FC}">
-          <x14:formula1>
-            <xm:f>Parameters!$D$4:$D$238</xm:f>
-          </x14:formula1>
-          <xm:sqref>E1:E1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
